--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED21.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED21.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>129W</t>
+          <t>158W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N4"/>
+  <dimension ref="B2:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -917,18 +917,6 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>贷款时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2季</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>160W</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L6"/>
+  <dimension ref="B2:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1712,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0138</t>
+          <t>SIM_XA_FIXED-4-0121</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1726,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33W</t>
+          <t>82W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1740,12 +1728,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第2年</t>
+          <t>第4年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1760,117 +1748,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年3季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0068</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>160W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0114</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>42W</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>4季</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G56"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2208,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2220,7 +2098,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,14 +2134,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Auction_Win</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2272,7 +2150,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
         </is>
       </c>
     </row>
@@ -2289,11 +2167,11 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年2季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2315,11 +2193,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2334,14 +2212,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2350,7 +2228,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2360,14 +2238,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E20" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2376,7 +2254,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2402,7 +2280,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2412,23 +2290,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2438,14 +2316,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E23" t="n">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2454,7 +2332,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-d255e0b101", "line_id": "L-d91f48031f", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2464,14 +2342,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2480,7 +2358,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2497,11 +2375,11 @@
         <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2523,11 +2401,11 @@
         <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2542,23 +2420,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0138", "receivable_term_quarters": 0, "revenue_wan": 33.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2568,23 +2446,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E28" t="n">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
         </is>
       </c>
     </row>
@@ -2594,23 +2472,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-545c998929", "line_id": "L-d91f48031f", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2620,23 +2498,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2646,23 +2524,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E31" t="n">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2672,23 +2550,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2698,23 +2576,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="E33" t="n">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2724,23 +2602,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E34" t="n">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-217e285404", "line_id": "L-d91f48031f", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2750,23 +2628,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E35" t="n">
-        <v>307</v>
+        <v>240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2783,11 +2661,11 @@
         <v>-14</v>
       </c>
       <c r="E36" t="n">
-        <v>293</v>
+        <v>226</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2806,19 +2684,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E37" t="n">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0114", "receivable_term_quarters": 4, "revenue_wan": 42.0}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0121", "receivable_term_quarters": 0, "revenue_wan": 82.0}</t>
         </is>
       </c>
     </row>
@@ -2832,19 +2710,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
       <c r="E38" t="n">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2858,19 +2736,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
       <c r="E39" t="n">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-217e285404", "line_id": "L-d91f48031f", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-6fd1bc2f5c", "line_id": "L-d91f48031f", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2887,11 +2765,11 @@
         <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2906,23 +2784,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E41" t="n">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
         </is>
       </c>
     </row>
@@ -2932,14 +2810,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2948,7 +2826,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2958,14 +2836,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2974,7 +2852,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2984,23 +2862,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E44" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -3010,23 +2888,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3036,23 +2914,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3062,23 +2940,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-404987f88b", "line_id": "L-d91f48031f", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3088,23 +2966,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
         </is>
       </c>
     </row>
@@ -3114,23 +2992,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3140,177 +3018,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>receivable_collected | {"receivable_id": "AR-5ae81d26c2"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E51" t="n">
-        <v>158</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Sell_Product</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>158</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0068", "receivable_term_quarters": 3, "revenue_wan": 160.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E53" t="n">
-        <v>144</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E54" t="n">
-        <v>129</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-d91f48031f"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>129</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-d91f48031f", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>53</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>129</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-d91f48031f", "asset_type": "production_line"}</t>
         </is>
@@ -3417,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3642,16 +3364,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3707,13 +3429,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="H16" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3732,13 +3454,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3757,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3779,16 +3501,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -3804,16 +3526,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-83</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="G20" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H20" t="n">
         <v>-61</v>
-      </c>
-      <c r="H20" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -3854,16 +3576,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-85.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G22" t="n">
+        <v>-68.2</v>
+      </c>
+      <c r="H22" t="n">
         <v>-76.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3904,16 +3626,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-98.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-85.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G24" t="n">
+        <v>-68.2</v>
+      </c>
+      <c r="H24" t="n">
         <v>-76.2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3954,16 +3676,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-98.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-85.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G26" t="n">
+        <v>-68.2</v>
+      </c>
+      <c r="H26" t="n">
         <v>-76.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -4053,16 +3775,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F30" t="n">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G30" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H30" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31">
@@ -4084,10 +3806,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4109,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4131,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -4178,16 +3900,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F35" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="G35" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H35" t="n">
-        <v>289</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36">
@@ -4303,16 +4025,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>490.6</v>
+        <v>488.6</v>
       </c>
       <c r="F40" t="n">
-        <v>405.4</v>
+        <v>398.4</v>
       </c>
       <c r="G40" t="n">
-        <v>329.2</v>
+        <v>330.2</v>
       </c>
       <c r="H40" t="n">
-        <v>325</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41">
@@ -4481,13 +4203,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-184.4</v>
+        <v>-186.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-269.6</v>
+        <v>-276.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-345.8</v>
+        <v>-344.8</v>
       </c>
     </row>
     <row r="48">
@@ -4503,16 +4225,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-98.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-85.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G48" t="n">
+        <v>-68.2</v>
+      </c>
+      <c r="H48" t="n">
         <v>-76.2</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-4.199999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4528,16 +4250,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>490.6</v>
+        <v>488.6</v>
       </c>
       <c r="F49" t="n">
-        <v>405.4</v>
+        <v>398.4</v>
       </c>
       <c r="G49" t="n">
-        <v>329.2</v>
+        <v>330.2</v>
       </c>
       <c r="H49" t="n">
-        <v>325</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50">
@@ -4553,16 +4275,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>490.6</v>
+        <v>488.6</v>
       </c>
       <c r="F50" t="n">
-        <v>405.4</v>
+        <v>398.4</v>
       </c>
       <c r="G50" t="n">
-        <v>329.2</v>
+        <v>330.2</v>
       </c>
       <c r="H50" t="n">
-        <v>325</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4633,7 +4355,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4782,7 +4504,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4931,7 +4653,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5080,7 +4802,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5229,7 +4951,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
